--- a/order_generation/PO_excel_selected/48-82P3-QSFG.xlsx
+++ b/order_generation/PO_excel_selected/48-82P3-QSFG.xlsx
@@ -2034,9 +2034,9 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
